--- a/data/歌单.xlsx
+++ b/data/歌单.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="558">
   <si>
     <t>Sunshine Girl - manaco</t>
   </si>
@@ -1685,6 +1685,9 @@
   </si>
   <si>
     <t>非原曲</t>
+  </si>
+  <si>
+    <t>跳过</t>
   </si>
 </sst>
 </file>
@@ -5712,95 +5715,119 @@
         <v>460</v>
       </c>
       <c r="B462" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
     </row>
     <row r="463" spans="1:2">
       <c r="A463" t="s">
         <v>461</v>
       </c>
+      <c r="B463" t="s">
+        <v>553</v>
+      </c>
     </row>
     <row r="464" spans="1:2">
       <c r="A464" t="s">
         <v>462</v>
       </c>
-    </row>
-    <row r="465" spans="1:1">
+      <c r="B464" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2">
       <c r="A465" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="466" spans="1:1">
+      <c r="B465" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2">
       <c r="A466" t="s">
         <v>463</v>
       </c>
-    </row>
-    <row r="467" spans="1:1">
+      <c r="B466" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2">
       <c r="A467" t="s">
         <v>464</v>
       </c>
-    </row>
-    <row r="468" spans="1:1">
+      <c r="B467" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2">
       <c r="A468" t="s">
         <v>465</v>
       </c>
-    </row>
-    <row r="469" spans="1:1">
+      <c r="B468" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2">
       <c r="A469" t="s">
         <v>466</v>
       </c>
-    </row>
-    <row r="470" spans="1:1">
+      <c r="B469" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2">
       <c r="A470" t="s">
         <v>467</v>
       </c>
-    </row>
-    <row r="471" spans="1:1">
+      <c r="B470" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2">
       <c r="A471" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="472" spans="1:1">
+    <row r="472" spans="1:2">
       <c r="A472" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="473" spans="1:1">
+    <row r="473" spans="1:2">
       <c r="A473" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="474" spans="1:1">
+    <row r="474" spans="1:2">
       <c r="A474" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="475" spans="1:1">
+    <row r="475" spans="1:2">
       <c r="A475" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="476" spans="1:1">
+    <row r="476" spans="1:2">
       <c r="A476" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="477" spans="1:1">
+    <row r="477" spans="1:2">
       <c r="A477" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="478" spans="1:1">
+    <row r="478" spans="1:2">
       <c r="A478" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="479" spans="1:1">
+    <row r="479" spans="1:2">
       <c r="A479" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="480" spans="1:1">
+    <row r="480" spans="1:2">
       <c r="A480" t="s">
         <v>477</v>
       </c>
